--- a/Rubrica Trabajo en grupo PAU.xlsx
+++ b/Rubrica Trabajo en grupo PAU.xlsx
@@ -404,6 +404,45 @@
   </si>
   <si>
     <t>Columna1</t>
+  </si>
+  <si>
+    <t>Ver procedures con COMMIT/ROLLBACK en PrimeraEntrega y PK_ASIGNA en SegundaEntrega</t>
+  </si>
+  <si>
+    <t>Ver bloques EXCEPTION en procedures de Primera, Segunda y Tercera Entrega</t>
+  </si>
+  <si>
+    <t>Ver archivo Pruebas_Completas.sql con 20 pruebas funcionales</t>
+  </si>
+  <si>
+    <t>Ver procedure DESPISTE en TerceraEntraga+Seguridad.sql linea 354</t>
+  </si>
+  <si>
+    <t>Ver procedure MIGRAR_CENTRO en TerceraEntraga+Seguridad.sql linea 416</t>
+  </si>
+  <si>
+    <t>Ver CHECK en AULA, ASISTENCIA, EXAMEN, CENTRO, ESTUDIANTE y VOCAL</t>
+  </si>
+  <si>
+    <t>Ver PK, UNIQUE INDEX y NOT NULL en definiciones de tablas</t>
+  </si>
+  <si>
+    <t>Ver FN_ESTUDIANTE_VPD y DBMS_RLS.ADD_POLICY en TerceraEntrega</t>
+  </si>
+  <si>
+    <t>Ver AUDIT POLICY audit_asistencia_updates y TR_AUDIT_ASISTENCIA</t>
+  </si>
+  <si>
+    <t>Ver inserts de VOCALES, MATERIAS, SEDES, ESTUDIANTES y CENTROS</t>
+  </si>
+  <si>
+    <t>Ver IDX_ESTUDIANTE_APELLIDOS_UP (UPPER) en SegundaEntrega</t>
+  </si>
+  <si>
+    <t>Ver LOG_ASISTENCIA, TR_AUDIT_ASISTENCIA, TR_MIGRAR_CENTRO, V_MI_SEDE_GESTION, DESPISTE</t>
+  </si>
+  <si>
+    <t>Nota final: 1.8</t>
   </si>
 </sst>
 </file>
@@ -921,7 +960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
@@ -1575,13 +1614,15 @@
         <v>81</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>105</v>
+      </c>
       <c r="F34" s="26"/>
-      <c r="G34" s="14">
+      <c r="G34" s="14" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="32.25" customHeight="1">
@@ -1596,13 +1637,15 @@
         <v>84</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>106</v>
+      </c>
       <c r="F35" s="26"/>
-      <c r="G35" s="14">
+      <c r="G35" s="14" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -1615,9 +1658,11 @@
       </c>
       <c r="C36" s="27"/>
       <c r="D36" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="28"/>
+        <v>10</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>107</v>
+      </c>
       <c r="F36" s="28"/>
       <c r="G36" s="29"/>
     </row>
@@ -1628,9 +1673,9 @@
       <c r="D37" s="16"/>
       <c r="E37" s="26"/>
       <c r="F37" s="26"/>
-      <c r="G37" s="30">
+      <c r="G37" s="30" t="n">
         <f>SUM(G6:G36)/COUNT(G6:G36)*1.5</f>
-        <v>1.396551724</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -1678,13 +1723,15 @@
         <v>90</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>108</v>
+      </c>
       <c r="F41" s="26"/>
-      <c r="G41" s="14">
+      <c r="G41" s="14" t="n">
         <f t="shared" ref="G41:G49" si="4">IF(D41="SI",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -1694,13 +1741,15 @@
         <v>91</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>109</v>
+      </c>
       <c r="F42" s="26"/>
-      <c r="G42" s="14">
+      <c r="G42" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -1715,13 +1764,15 @@
         <v>93</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>110</v>
+      </c>
       <c r="F43" s="26"/>
-      <c r="G43" s="14">
+      <c r="G43" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -1731,13 +1782,15 @@
         <v>94</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>111</v>
+      </c>
       <c r="F44" s="26"/>
-      <c r="G44" s="14">
+      <c r="G44" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
@@ -1752,13 +1805,15 @@
         <v>95</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>112</v>
+      </c>
       <c r="F45" s="26"/>
-      <c r="G45" s="14">
+      <c r="G45" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -1768,13 +1823,15 @@
         <v>96</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E46" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>113</v>
+      </c>
       <c r="F46" s="26"/>
-      <c r="G46" s="14">
+      <c r="G46" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -1784,13 +1841,15 @@
         <v>97</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>114</v>
+      </c>
       <c r="F47" s="26"/>
-      <c r="G47" s="14">
+      <c r="G47" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="48.75" customHeight="1">
@@ -1805,13 +1864,15 @@
         <v>99</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E48" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>115</v>
+      </c>
       <c r="F48" s="26"/>
-      <c r="G48" s="14">
+      <c r="G48" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -1826,13 +1887,15 @@
         <v>101</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E49" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>116</v>
+      </c>
       <c r="F49" s="26"/>
-      <c r="G49" s="14">
+      <c r="G49" s="14" t="n">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" ht="45.0" customHeight="1">
@@ -1854,9 +1917,9 @@
       <c r="D51" s="14"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
-      <c r="G51" s="30">
+      <c r="G51" s="30" t="n">
         <f>G50+G37</f>
-        <v>1.396551724</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -1893,7 +1956,7 @@
         <v>102</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
